--- a/booking_forms/039_film_pitch_presentation_booking_form--booking_forms.xlsx
+++ b/booking_forms/039_film_pitch_presentation_booking_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>production_company</t>
+          <t>production_company_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Production Company</t>
+          <t>Production Company 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>project_status_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Project Status</t>
+          <t>Project Status 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>production_status</t>
+          <t>production_status_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Production Status</t>
+          <t>Production Status 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>presenter</t>
+          <t>presenter_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Presenter</t>
+          <t>Presenter 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>production_company</t>
+          <t>production_company_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Production Company</t>
+          <t>Production Company 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Event 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>project_type_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Project Type</t>
+          <t>Project Type 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'abc_production'}</t>
+          <t>abc_production</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'ABC Production'}</t>
+          <t>ABC Production</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'def_productions'}</t>
+          <t>def_productions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'DEF Productions'}</t>
+          <t>DEF Productions</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'ghi_productions'}</t>
+          <t>ghi_productions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'GHI Productions'}</t>
+          <t>GHI Productions</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'8:00_am'}</t>
+          <t>8:00_am</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '8:00 AM'}</t>
+          <t>8:00 AM</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'9:00_am'}</t>
+          <t>9:00_am</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '9:00 AM'}</t>
+          <t>9:00 AM</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'10:00_am'}</t>
+          <t>10:00_am</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '10:00 AM'}</t>
+          <t>10:00 AM</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1352,63 +1352,63 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'john_smith'}</t>
+          <t>john_smith</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'John Smith'}</t>
+          <t>John Smith</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>production_company_choices</t>
+          <t>production_company_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'abc_production'}</t>
+          <t>abc_production</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'ABC Production'}</t>
+          <t>ABC Production</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>production_company_choices</t>
+          <t>production_company_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'def_production'}</t>
+          <t>def_production</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'DEF Production'}</t>
+          <t>DEF Production</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>production_company_choices</t>
+          <t>production_company_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'ghi_production'}</t>
+          <t>ghi_production</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'GHI Production'}</t>
+          <t>GHI Production</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'film_festival'}</t>
+          <t>film_festival</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Film Festival'}</t>
+          <t>Film Festival</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'film_market'}</t>
+          <t>film_market</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Film Market'}</t>
+          <t>Film Market</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'film_pitch'}</t>
+          <t>film_pitch</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Film Pitch'}</t>
+          <t>Film Pitch</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'animation'}</t>
+          <t>animation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Animation'}</t>
+          <t>Animation</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'live_action'}</t>
+          <t>live_action</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Live Action'}</t>
+          <t>Live Action</t>
         </is>
       </c>
     </row>
@@ -1505,301 +1505,301 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'documentary'}</t>
+          <t>documentary</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Documentary'}</t>
+          <t>Documentary</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>production_status_choices</t>
+          <t>production_status_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>production_status_choices</t>
+          <t>production_status_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>production_status_choices</t>
+          <t>production_status_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>presenter_choices</t>
+          <t>presenter_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>presenter_choices</t>
+          <t>presenter_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'john_smith'}</t>
+          <t>john_smith</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'John Smith'}</t>
+          <t>John Smith</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>production_company_choices</t>
+          <t>production_company_3_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'abc_production'}</t>
+          <t>abc_production</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'ABC Production'}</t>
+          <t>ABC Production</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>production_company_choices</t>
+          <t>production_company_3_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'def_production'}</t>
+          <t>def_production</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'DEF Production'}</t>
+          <t>DEF Production</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>production_company_choices</t>
+          <t>production_company_3_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'ghi_production'}</t>
+          <t>ghi_production</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'GHI Production'}</t>
+          <t>GHI Production</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>event_choices</t>
+          <t>event_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'film_festival'}</t>
+          <t>film_festival</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Film Festival'}</t>
+          <t>Film Festival</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>event_choices</t>
+          <t>event_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'film_market'}</t>
+          <t>film_market</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Film Market'}</t>
+          <t>Film Market</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>event_choices</t>
+          <t>event_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'film_pitch'}</t>
+          <t>film_pitch</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Film Pitch'}</t>
+          <t>Film Pitch</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>project_type_choices</t>
+          <t>project_type_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'animation'}</t>
+          <t>animation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Animation'}</t>
+          <t>Animation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>project_type_choices</t>
+          <t>project_type_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'live_action'}</t>
+          <t>live_action</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Live Action'}</t>
+          <t>Live Action</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>project_type_choices</t>
+          <t>project_type_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'documentary'}</t>
+          <t>documentary</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Documentary'}</t>
+          <t>Documentary</t>
         </is>
       </c>
     </row>
